--- a/dataset/construct/dataset_splits/data_size/10_percent/tum/fold5.xlsx
+++ b/dataset/construct/dataset_splits/data_size/10_percent/tum/fold5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>495</v>
+        <v>597</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,123 +625,112 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>74.7334821722818</v>
+        <v>80.8852175070348</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>24.9680097375237</v>
       </c>
       <c r="E2" t="n">
-        <v>30.1102788964582</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>532</v>
       </c>
       <c r="I2" t="n">
-        <v>461</v>
+        <v>615</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>593</v>
       </c>
       <c r="K2" t="n">
-        <v>575</v>
+        <v>1740</v>
       </c>
       <c r="L2" t="n">
-        <v>273</v>
+        <v>35</v>
       </c>
       <c r="M2" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1072</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="P2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="V2" t="n">
-        <v>18</v>
+        <v>0.19</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>28.6478227654698</v>
       </c>
       <c r="X2" t="n">
-        <v>24.35</v>
+        <v>27.9784080907002</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15530303030303</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.1914947797301</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>23.7726133940886</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>148</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1736</v>
+        <v>2169</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -764,91 +738,91 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>86.46788494689081</v>
+        <v>79.1083821646767</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>23.1836734693877</v>
       </c>
       <c r="E3" t="n">
-        <v>24.8579545454545</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>696.4</v>
       </c>
       <c r="I3" t="n">
-        <v>4130</v>
+        <v>556.8</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>561.3</v>
       </c>
       <c r="K3" t="n">
-        <v>187.8</v>
+        <v>1814.5</v>
       </c>
       <c r="L3" t="n">
-        <v>186.2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>239</v>
+        <v>44.3</v>
       </c>
       <c r="N3" t="n">
-        <v>613</v>
+        <v>52.8</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>25.25</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>25.6557168321874</v>
       </c>
       <c r="X3" t="n">
-        <v>27.2</v>
+        <v>24.2129335077053</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.192691029900332</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>27.3745861981156</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>26.9117274486368</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -863,22 +837,13 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>96</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>368</v>
+        <v>528</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -886,77 +851,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74.1969855755824</v>
+        <v>84.2009601490608</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>20.5498866213151</v>
       </c>
       <c r="E4" t="n">
-        <v>26.0261748958953</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>118.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>74.2</v>
+      </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>1100</v>
+        <v>275</v>
       </c>
       <c r="L4" t="n">
-        <v>297</v>
+        <v>35.2</v>
       </c>
       <c r="M4" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1657</v>
+        <v>6.5</v>
       </c>
       <c r="O4" t="n">
-        <v>33</v>
+        <v>41.7</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>60</v>
+        <v>13.8</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>22.8545963840081</v>
       </c>
       <c r="X4" t="n">
-        <v>22.35</v>
+        <v>22.0850401322991</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.226190476190476</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.9182582123759</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>22.3940969210825</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -971,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -983,24 +950,15 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>124</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>754</v>
+        <v>2375</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1008,88 +966,88 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>65.49301657920751</v>
+        <v>85.331470485715</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>23.4567901234567</v>
       </c>
       <c r="E5" t="n">
-        <v>31.2100121719047</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>38.3</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
+        <v>121.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1730</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>197.3</v>
       </c>
       <c r="K5" t="n">
-        <v>283</v>
+        <v>388.1</v>
       </c>
       <c r="L5" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>284</v>
+        <v>5.4</v>
       </c>
       <c r="N5" t="n">
-        <v>776</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>27</v>
+        <v>14.6</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>44</v>
+        <v>24.25</v>
       </c>
       <c r="V5" t="n">
-        <v>44</v>
+        <v>0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>24.7326203208556</v>
       </c>
       <c r="X5" t="n">
-        <v>23.4</v>
+        <v>24.3805715703063</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.279411764705882</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.2365673542144</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.8163986665956</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1098,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1107,24 +1065,13 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN5" t="n">
         <v>142</v>
       </c>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2006</v>
+        <v>2319</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1132,85 +1079,85 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67.10314342662311</v>
+        <v>77.2493207024615</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>28.515625</v>
       </c>
       <c r="E6" t="n">
-        <v>33.8123415046491</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>55.8</v>
       </c>
       <c r="I6" t="n">
-        <v>391</v>
+        <v>46.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>14.9</v>
       </c>
       <c r="K6" t="n">
-        <v>718.6</v>
+        <v>117.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1023.4</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>535.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2277.8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>140.7</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>59.7</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>252.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>100.6</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>22.8</v>
       </c>
       <c r="V6" t="n">
-        <v>105.6</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>22.5362872421696</v>
       </c>
       <c r="X6" t="n">
-        <v>27.2</v>
+        <v>22.1741916431478</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0912280701754387</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>27.6610644257703</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>27.3480481672903</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1219,36 +1166,27 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>92</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>226</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1256,88 +1194,88 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>82.4873716632443</v>
+        <v>86.8191345349456</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>25.6055363321799</v>
       </c>
       <c r="E7" t="n">
-        <v>24.4897959183673</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
+        <v>420</v>
       </c>
       <c r="I7" t="n">
-        <v>18300</v>
+        <v>285</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>308</v>
       </c>
       <c r="K7" t="n">
-        <v>694</v>
+        <v>1013</v>
       </c>
       <c r="L7" t="n">
-        <v>856</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2609</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>23.8</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>23.554876496053</v>
       </c>
       <c r="X7" t="n">
-        <v>25.3</v>
+        <v>23.4220054480732</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.255172413793103</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>26.4196587726</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>25.6028939368547</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1346,27 +1284,20 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>126</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
+        <v>190</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
